--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70b5eb17ece67e4a/Desktop/itvedanth/Demart/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/70B5EB17ECE67E4A/Desktop/itvedanth/Demart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="8_{2D6787B3-06BA-4AFF-8092-9F33494D2932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F22DF1AA-1ACD-4346-BDDD-D63B62FF61D1}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="8_{2D6787B3-06BA-4AFF-8092-9F33494D2932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{222E9BD6-9398-4E31-B31A-BE743EE5B1BE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{F7DBB859-EC45-4620-9987-D900FBE4D7E1}"/>
+    <workbookView xWindow="3768" yWindow="3540" windowWidth="17280" windowHeight="9420" xr2:uid="{F7DBB859-EC45-4620-9987-D900FBE4D7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,95 +38,87 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
-  <si>
-    <t>Sales Person</t>
-  </si>
-  <si>
-    <t>Region</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sales </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arjun </t>
-  </si>
-  <si>
-    <t>North</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Priya </t>
-  </si>
-  <si>
-    <t>South</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rahul </t>
-  </si>
-  <si>
-    <t>East</t>
-  </si>
-  <si>
-    <t>Ananya</t>
-  </si>
-  <si>
-    <t>West</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vikram </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sneha </t>
-  </si>
-  <si>
-    <t>Karthik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meera </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aditya </t>
-  </si>
-  <si>
-    <t>Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kavya </t>
-  </si>
-  <si>
-    <t>Region  East</t>
-  </si>
-  <si>
-    <t>Region  West</t>
-  </si>
-  <si>
-    <t>Region North</t>
-  </si>
-  <si>
-    <t>Region South</t>
-  </si>
-  <si>
-    <t>MI</t>
-  </si>
-  <si>
-    <t>CSK</t>
-  </si>
-  <si>
-    <t>GT</t>
-  </si>
-  <si>
-    <t>KKR</t>
-  </si>
-  <si>
-    <t>RCB</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+  <si>
+    <t>Colors</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Enter the color</t>
+  </si>
+  <si>
+    <t>green</t>
+  </si>
+  <si>
+    <t>Index=</t>
+  </si>
+  <si>
+    <t>Enter The Position</t>
+  </si>
+  <si>
+    <t>Employee Data</t>
+  </si>
+  <si>
+    <t>Eno.</t>
+  </si>
+  <si>
+    <t>Ename</t>
+  </si>
+  <si>
+    <t>Esalary</t>
+  </si>
+  <si>
+    <t>Person 1</t>
+  </si>
+  <si>
+    <t>Person 2</t>
+  </si>
+  <si>
+    <t>Person 3</t>
+  </si>
+  <si>
+    <t>Input</t>
+  </si>
+  <si>
+    <t>Employe salary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,16 +134,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -159,13 +163,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -181,6 +211,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -500,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91728A69-EBBF-4619-9614-7626513BEEB0}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
@@ -510,204 +544,168 @@
     <col min="12" max="12" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="G6">
+        <f>IFERROR(MATCH(G5,B5:B7,0),"Not Found")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>12500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>18200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="G9" t="str" cm="1">
+        <f t="array" ref="G9">INDEX(B5:B7,G6)</f>
+        <v>Green</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q11" s="4"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G12" t="str" cm="1">
+        <f t="array" ref="G12:G14">IFERROR(MATCH(B5:B7,E15),"NF")</f>
+        <v>NF</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G13" t="str">
+        <v>NF</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="G14" t="str">
+        <v>NF</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>9750</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>21400</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>15600</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="L6">
-        <f>COUNTIFS(B2:B11,"North",C2:C11,"&gt;15000")</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="E15">
+        <v>7</v>
+      </c>
+      <c r="J15" s="3">
+        <v>101</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7">
-        <v>13900</v>
-      </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="L15" s="3">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="J16" s="3">
+        <v>102</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8">
-        <v>17300</v>
-      </c>
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="L16" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="17" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J17" s="3">
+        <v>103</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9">
-        <v>24100</v>
-      </c>
-      <c r="F9" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="L17" s="3">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="18" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+    </row>
+    <row r="19" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+    </row>
+    <row r="20" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J20" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B10" t="s">
+      <c r="K20" s="5"/>
+      <c r="L20" s="3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+    </row>
+    <row r="22" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="J22" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C10">
-        <v>11800</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11">
-        <v>19500</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H15">
-        <v>2020</v>
-      </c>
-      <c r="I15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="H16">
-        <v>2021</v>
-      </c>
-      <c r="I16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="8:12" x14ac:dyDescent="0.3">
-      <c r="H17">
-        <v>2022</v>
-      </c>
-      <c r="I17" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17">
-        <f>COUNTIF(I15:I21,"CSK")</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="8:12" x14ac:dyDescent="0.3">
-      <c r="H18">
-        <v>2023</v>
-      </c>
-      <c r="I18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="8:12" x14ac:dyDescent="0.3">
-      <c r="H19">
-        <v>2024</v>
-      </c>
-      <c r="I19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="8:12" x14ac:dyDescent="0.3">
-      <c r="H20">
-        <v>2025</v>
-      </c>
-      <c r="I20" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="21" spans="8:12" x14ac:dyDescent="0.3">
-      <c r="H21">
-        <v>2026</v>
-      </c>
-      <c r="I21" t="s">
-        <v>26</v>
+      <c r="K22" s="6"/>
+      <c r="L22" s="3">
+        <f>INDEX(L15:L17,MATCH(L20,J15:J17,0))</f>
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="26" spans="10:12" x14ac:dyDescent="0.3">
+      <c r="L26">
+        <f>INDEX(L15:L17,MATCH(L20,J15:J17,0))</f>
+        <v>40000</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J22:K22"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>